--- a/output/pdf_financials_xlsx/ALGR.xlsx
+++ b/output/pdf_financials_xlsx/ALGR.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.187848</v>
+        <v>0.067067</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.033578</v>
+        <v>0.004114</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.004046</v>
@@ -1649,7 +1649,7 @@
         <v>0.024752</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.214058</v>
+        <v>0.008952</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.971071</v>
@@ -1668,10 +1668,12 @@
         <v>0.033578</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.004046</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.024752</v>
+        <v>0.051897</v>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="3" t="n">
         <v>0.22301</v>
@@ -1980,10 +1982,10 @@
         <v>0.013021</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.047851</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.27299</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -2005,10 +2007,12 @@
         <v>3.845266</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.047851</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>1.27299</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>0</v>
@@ -2750,13 +2754,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.159027</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.155848</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.155153</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
@@ -2775,22 +2779,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.445068</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.481634</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.481634</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.481634</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.481634</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.730632</v>
       </c>
     </row>
     <row r="93">
@@ -4502,7 +4506,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4546,7 +4554,11 @@
           <t>Share based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4786,7 +4798,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4972,7 +4984,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -5016,7 +5032,11 @@
           <t>Share based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -5392,7 +5412,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5434,7 +5458,11 @@
           <t>Share based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -5476,7 +5504,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.159027</v>
       </c>
@@ -5798,7 +5830,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -6086,7 +6118,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>0.06374100000000001</v>
       </c>
@@ -6130,7 +6166,11 @@
           <t>Share based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>2.381327</v>
       </c>
@@ -8163,7 +8203,7 @@
         <v>-4.236325</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.862673</v>
+        <v>-0.862673</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALGR.xlsx
+++ b/output/pdf_financials_xlsx/ALGR.xlsx
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.120781</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.029464</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00718</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.27299</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.214058</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.289549</v>
       </c>
     </row>
     <row r="35">
@@ -1337,22 +1337,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.120781</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.029464</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00718</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.27299</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.214058</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.289549</v>
       </c>
     </row>
     <row r="37">
@@ -1643,16 +1643,16 @@
         <v>0.004114</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004046</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.024752</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.008952</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.971071</v>
+        <v>0.681522</v>
       </c>
     </row>
     <row r="49">
@@ -1668,12 +1668,10 @@
         <v>0.033578</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.051897</v>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004046</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.024752</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>0.22301</v>
@@ -1982,10 +1980,10 @@
         <v>0.013021</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0</v>
+        <v>0.047851</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0</v>
+        <v>1.27299</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -2007,12 +2005,10 @@
         <v>3.845266</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047851</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1.27299</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>0</v>
@@ -4050,7 +4046,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4798,7 +4794,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5830,7 +5826,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -10582,7 +10578,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALGR.xlsx
+++ b/output/pdf_financials_xlsx/ALGR.xlsx
@@ -937,7 +937,7 @@
         <v>-0.648865</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-4.236325</v>
+        <v>-0.41237</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.551455</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0388</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.044245</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.194001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.28091</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.027262</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.216914</v>
       </c>
     </row>
     <row r="68">
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.010468</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.036566</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -8638,7 +8638,11 @@
           <t>Share based payment expense</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.010468</v>
       </c>
@@ -9252,7 +9256,11 @@
           <t>Share based payment expense - - - - -</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -11474,7 +11482,11 @@
           <t>Net Loss from Continuing Operations</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
